--- a/tools/importer/reports/import-reports-and-presentations.report.xlsx
+++ b/tools/importer/reports/import-reports-and-presentations.report.xlsx
@@ -64,7 +64,7 @@
     <t>en/investors/reports-and-presentations.report.json</t>
   </si>
   <si>
-    <t>[]</t>
+    <t>["cards-feature"]</t>
   </si>
   <si>
     <t>en/investors/reports-and-presentations</t>
@@ -73,7 +73,7 @@
     <t>reports-and-presentations</t>
   </si>
   <si>
-    <t>2026-08-10T15:15:28.239Z</t>
+    <t>2026-08-10T16:24:17.541Z</t>
   </si>
   <si>
     <t>Reports and presentations</t>

--- a/tools/importer/reports/import-reports-and-presentations.report.xlsx
+++ b/tools/importer/reports/import-reports-and-presentations.report.xlsx
@@ -73,7 +73,7 @@
     <t>reports-and-presentations</t>
   </si>
   <si>
-    <t>2026-08-10T16:24:17.541Z</t>
+    <t>2026-08-10T16:41:25.724Z</t>
   </si>
   <si>
     <t>Reports and presentations</t>
